--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.1 客户基础信息/1. 客户信息.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.1 客户基础信息/1. 客户信息.xlsx
@@ -151,16 +151,16 @@
     <t>businessRule</t>
   </si>
   <si>
-    <t>referenceDoc</t>
-  </si>
-  <si>
-    <t>referenceCode</t>
+    <t>referenceDocument</t>
+  </si>
+  <si>
+    <t>referenceCommonCode</t>
   </si>
   <si>
     <t>subordinateDepartment</t>
   </si>
   <si>
-    <t>referenceNo</t>
+    <t>referenceNumber</t>
   </si>
   <si>
     <t>authoritySystem</t>
@@ -680,14 +680,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1238,48 +1231,51 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1289,117 +1285,120 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1413,14 +1412,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1428,7 +1424,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1441,12 +1440,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>

--- a/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.1 客户基础信息/1. 客户信息.xlsx
+++ b/dama/cases/营收系统数据标准/2 服务类/2.2 客户管理数据/2.2.1 客户基础信息/1. 客户信息.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="217">
   <si>
     <t>业务属性</t>
   </si>
@@ -304,172 +304,169 @@
     <t>与客户有效证件登记名称一致，不允许为空。</t>
   </si>
   <si>
+    <t>支持中文、大小写字母、数字、普通标点；禁止乱码控制字符，去除首尾空格</t>
+  </si>
+  <si>
+    <t>自由文本，最大长度100。</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>高</t>
+  </si>
+  <si>
+    <t>个人敏感信息</t>
+  </si>
+  <si>
+    <t>RCM_CUSTOMER_ADDRESS</t>
+  </si>
+  <si>
+    <t>客户完整地址</t>
+  </si>
+  <si>
+    <t>CUSTOMER_ADDRESS</t>
+  </si>
+  <si>
+    <t>客户用水/装表地址。</t>
+  </si>
+  <si>
+    <t>供水地址，须与各级地址、详细地址保持一致。</t>
+  </si>
+  <si>
+    <t>自由文本，最大长度200。</t>
+  </si>
+  <si>
+    <t>RCM_CUSTOMER_TYPE</t>
+  </si>
+  <si>
+    <t>客户类型</t>
+  </si>
+  <si>
+    <t>CUSTOMER_TYPE</t>
+  </si>
+  <si>
+    <t>客户分类编码，区分居民/非居民等用水性质。</t>
+  </si>
+  <si>
+    <t>取值以营业收费系统客户类型字典为准（0居民/1非居民）。</t>
+  </si>
+  <si>
+    <t>客户类型代码表</t>
+  </si>
+  <si>
+    <t>NUMBER</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0-居民、1-非居民</t>
+  </si>
+  <si>
+    <t>低</t>
+  </si>
+  <si>
+    <t>一般业务数据</t>
+  </si>
+  <si>
+    <t>RCM_CUSTOMER_INDUSTRY</t>
+  </si>
+  <si>
+    <t>行业</t>
+  </si>
+  <si>
+    <t>CUSTOMER_INDUSTRY</t>
+  </si>
+  <si>
+    <t>客户所属行业类别，用于非居民用户行业分类统计。</t>
+  </si>
+  <si>
+    <t>按国民经济行业分类填写。</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>自由文本，最大长度50；建议引用行业分类字典。</t>
+  </si>
+  <si>
+    <t>RCM_LEGAL_MASTER</t>
+  </si>
+  <si>
+    <t>户主（法人）</t>
+  </si>
+  <si>
+    <t>LEGAL_MASTER</t>
+  </si>
+  <si>
+    <t>客户户主或法人代表姓名。</t>
+  </si>
+  <si>
+    <t>个人客户填户主姓名，单位客户填法人代表。</t>
+  </si>
+  <si>
+    <t>自由文本，最大长度50。</t>
+  </si>
+  <si>
+    <t>RCM_CERTIFICATE_CODE</t>
+  </si>
+  <si>
+    <t>证件号码</t>
+  </si>
+  <si>
+    <t>CERTIFICATE_CODE</t>
+  </si>
+  <si>
+    <t>客户证件（身份证/统一社会信用代码等）号码。</t>
+  </si>
+  <si>
+    <t>身份证号或其他有效证件号，唯一。</t>
+  </si>
+  <si>
+    <t>自由文本，最大长度50；须与证件类型匹配。</t>
+  </si>
+  <si>
+    <t>RCM_CERTIFICATE_TYPE</t>
+  </si>
+  <si>
+    <t>证件类型</t>
+  </si>
+  <si>
+    <t>CERTIFICATE_TYPE</t>
+  </si>
+  <si>
+    <t>客户证件类型。</t>
+  </si>
+  <si>
+    <t>取值以证件类型字典为准。</t>
+  </si>
+  <si>
+    <t>证件类型代码表</t>
+  </si>
+  <si>
+    <t>1-身份证、2-护照、3-驾照</t>
+  </si>
+  <si>
+    <t>RCM_CONTACTS</t>
+  </si>
+  <si>
+    <t>联系人</t>
+  </si>
+  <si>
+    <t>CONTACTS</t>
+  </si>
+  <si>
+    <t>客户联系人编号。</t>
+  </si>
+  <si>
     <t>100</t>
-  </si>
-  <si>
-    <t>支持中文、大小写字母、数字、普通标点；禁止乱码控制字符，去除首尾空格</t>
-  </si>
-  <si>
-    <t>自由文本，最大长度100。</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>高</t>
-  </si>
-  <si>
-    <t>个人敏感信息</t>
-  </si>
-  <si>
-    <t>RCM_CUSTOMER_ADDRESS</t>
-  </si>
-  <si>
-    <t>客户完整地址</t>
-  </si>
-  <si>
-    <t>CUSTOMER_ADDRESS</t>
-  </si>
-  <si>
-    <t>客户用水/装表地址。</t>
-  </si>
-  <si>
-    <t>供水地址，须与各级地址、详细地址保持一致。</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>自由文本，最大长度200。</t>
-  </si>
-  <si>
-    <t>RCM_CUSTOMER_TYPE</t>
-  </si>
-  <si>
-    <t>客户类型</t>
-  </si>
-  <si>
-    <t>CUSTOMER_TYPE</t>
-  </si>
-  <si>
-    <t>客户分类编码，区分居民/非居民等用水性质。</t>
-  </si>
-  <si>
-    <t>取值以营业收费系统客户类型字典为准（0居民/1非居民）。</t>
-  </si>
-  <si>
-    <t>客户类型代码表</t>
-  </si>
-  <si>
-    <t>NUMBER</t>
-  </si>
-  <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>0-居民、1-非居民</t>
-  </si>
-  <si>
-    <t>低</t>
-  </si>
-  <si>
-    <t>一般业务数据</t>
-  </si>
-  <si>
-    <t>RCM_CUSTOMER_INDUSTRY</t>
-  </si>
-  <si>
-    <t>行业</t>
-  </si>
-  <si>
-    <t>CUSTOMER_INDUSTRY</t>
-  </si>
-  <si>
-    <t>客户所属行业类别，用于非居民用户行业分类统计。</t>
-  </si>
-  <si>
-    <t>按国民经济行业分类填写。</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>自由文本，最大长度50；建议引用行业分类字典。</t>
-  </si>
-  <si>
-    <t>RCM_LEGAL_MASTER</t>
-  </si>
-  <si>
-    <t>户主（法人）</t>
-  </si>
-  <si>
-    <t>LEGAL_MASTER</t>
-  </si>
-  <si>
-    <t>客户户主或法人代表姓名。</t>
-  </si>
-  <si>
-    <t>个人客户填户主姓名，单位客户填法人代表。</t>
-  </si>
-  <si>
-    <t>自由文本，最大长度50。</t>
-  </si>
-  <si>
-    <t>RCM_CERTIFICATE_CODE</t>
-  </si>
-  <si>
-    <t>证件号码</t>
-  </si>
-  <si>
-    <t>CERTIFICATE_CODE</t>
-  </si>
-  <si>
-    <t>客户证件（身份证/统一社会信用代码等）号码。</t>
-  </si>
-  <si>
-    <t>身份证号或其他有效证件号，唯一。</t>
-  </si>
-  <si>
-    <t>自由文本，最大长度50；须与证件类型匹配。</t>
-  </si>
-  <si>
-    <t>RCM_CERTIFICATE_TYPE</t>
-  </si>
-  <si>
-    <t>证件类型</t>
-  </si>
-  <si>
-    <t>CERTIFICATE_TYPE</t>
-  </si>
-  <si>
-    <t>客户证件类型。</t>
-  </si>
-  <si>
-    <t>取值以证件类型字典为准。</t>
-  </si>
-  <si>
-    <t>证件类型代码表</t>
-  </si>
-  <si>
-    <t>1-身份证、2-护照、3-驾照</t>
-  </si>
-  <si>
-    <t>RCM_CONTACTS</t>
-  </si>
-  <si>
-    <t>联系人</t>
-  </si>
-  <si>
-    <t>CONTACTS</t>
-  </si>
-  <si>
-    <t>客户联系人编号。</t>
   </si>
   <si>
     <t>RCM_MOBILE</t>
@@ -2163,8 +2160,8 @@
       <c r="Q5" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R5" s="6" t="s">
-        <v>96</v>
+      <c r="R5" s="6">
+        <v>400</v>
       </c>
       <c r="S5" s="6"/>
       <c r="T5" s="6"/>
@@ -2184,30 +2181,30 @@
         <v>85</v>
       </c>
       <c r="Z5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="AA5" s="6" t="s">
+      <c r="AB5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="AB5" s="6" t="s">
+      <c r="AC5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AC5" s="6" t="s">
+      <c r="AD5" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="AD5" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:30">
       <c r="A6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>69</v>
@@ -2222,10 +2219,10 @@
         <v>72</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6"/>
@@ -2245,8 +2242,8 @@
       <c r="Q6" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R6" s="6" t="s">
-        <v>107</v>
+      <c r="R6" s="6">
+        <v>800</v>
       </c>
       <c r="S6" s="6"/>
       <c r="T6" s="6"/>
@@ -2266,10 +2263,10 @@
         <v>85</v>
       </c>
       <c r="Z6" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="AB6" s="6" t="s">
         <v>88</v>
@@ -2283,13 +2280,13 @@
     </row>
     <row r="7" ht="72" spans="1:30">
       <c r="A7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>69</v>
@@ -2304,14 +2301,14 @@
         <v>72</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>75</v>
@@ -2324,16 +2321,16 @@
         <v>77</v>
       </c>
       <c r="P7" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="S7" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="S7" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="T7" s="6"/>
       <c r="U7" s="6" t="s">
@@ -2355,27 +2352,27 @@
         <v>86</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AB7" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD7" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" ht="72" spans="1:30">
       <c r="A8" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>69</v>
@@ -2390,10 +2387,10 @@
         <v>72</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
@@ -2414,7 +2411,7 @@
         <v>79</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
@@ -2434,30 +2431,30 @@
         <v>85</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="AB8" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC8" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD8" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" ht="72" spans="1:30">
       <c r="A9" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>129</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>69</v>
@@ -2472,10 +2469,10 @@
         <v>72</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
@@ -2495,8 +2492,8 @@
       <c r="Q9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="R9" s="6" t="s">
-        <v>127</v>
+      <c r="R9" s="6">
+        <v>200</v>
       </c>
       <c r="S9" s="6"/>
       <c r="T9" s="6"/>
@@ -2516,30 +2513,30 @@
         <v>85</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB9" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC9" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AC9" s="6" t="s">
+      <c r="AD9" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="AD9" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="10" ht="72" spans="1:30">
       <c r="A10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>69</v>
@@ -2554,10 +2551,10 @@
         <v>72</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
@@ -2578,7 +2575,7 @@
         <v>79</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S10" s="6"/>
       <c r="T10" s="6"/>
@@ -2601,27 +2598,27 @@
         <v>86</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AB10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC10" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AC10" s="6" t="s">
+      <c r="AD10" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="AD10" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="11" ht="72" spans="1:30">
       <c r="A11" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>141</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>69</v>
@@ -2636,14 +2633,14 @@
         <v>72</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>75</v>
@@ -2656,16 +2653,16 @@
         <v>77</v>
       </c>
       <c r="P11" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="S11" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="S11" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="T11" s="6"/>
       <c r="U11" s="6" t="s">
@@ -2684,13 +2681,13 @@
         <v>85</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA11" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AB11" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC11" s="6" t="s">
         <v>89</v>
@@ -2701,13 +2698,13 @@
     </row>
     <row r="12" ht="72" spans="1:30">
       <c r="A12" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>69</v>
@@ -2722,10 +2719,10 @@
         <v>72</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6"/>
@@ -2746,7 +2743,7 @@
         <v>79</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -2766,13 +2763,13 @@
         <v>85</v>
       </c>
       <c r="Z12" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA12" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="AA12" s="6" t="s">
+      <c r="AB12" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="AB12" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="AC12" s="6" t="s">
         <v>89</v>
@@ -2783,13 +2780,13 @@
     </row>
     <row r="13" ht="72" spans="1:30">
       <c r="A13" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>153</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>154</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>69</v>
@@ -2804,10 +2801,10 @@
         <v>72</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>156</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
@@ -2828,7 +2825,7 @@
         <v>79</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S13" s="6"/>
       <c r="T13" s="6"/>
@@ -2848,30 +2845,30 @@
         <v>85</v>
       </c>
       <c r="Z13" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA13" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="AA13" s="6" t="s">
-        <v>158</v>
-      </c>
       <c r="AB13" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="AC13" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="AC13" s="6" t="s">
+      <c r="AD13" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="AD13" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="14" ht="72" spans="1:30">
       <c r="A14" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>69</v>
@@ -2886,10 +2883,10 @@
         <v>72</v>
       </c>
       <c r="H14" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>163</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6"/>
@@ -2910,7 +2907,7 @@
         <v>79</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S14" s="6"/>
       <c r="T14" s="6"/>
@@ -2930,13 +2927,13 @@
         <v>85</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AB14" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC14" s="6" t="s">
         <v>89</v>
@@ -2947,13 +2944,13 @@
     </row>
     <row r="15" ht="72" spans="1:30">
       <c r="A15" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>69</v>
@@ -2968,10 +2965,10 @@
         <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>168</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
@@ -2992,7 +2989,7 @@
         <v>79</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="S15" s="6"/>
       <c r="T15" s="6"/>
@@ -3012,30 +3009,30 @@
         <v>85</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA15" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AB15" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD15" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" ht="72" spans="1:30">
       <c r="A16" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>174</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>69</v>
@@ -3050,10 +3047,10 @@
         <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>175</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>176</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
@@ -3074,7 +3071,7 @@
         <v>79</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
@@ -3094,13 +3091,13 @@
         <v>85</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AB16" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AC16" s="6" t="s">
         <v>89</v>
@@ -3111,13 +3108,13 @@
     </row>
     <row r="17" ht="72" spans="1:30">
       <c r="A17" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>69</v>
@@ -3132,10 +3129,10 @@
         <v>72</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
@@ -3150,13 +3147,13 @@
         <v>77</v>
       </c>
       <c r="P17" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Q17" s="6" t="s">
         <v>79</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
@@ -3176,13 +3173,13 @@
         <v>85</v>
       </c>
       <c r="Z17" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA17" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="AA17" s="6" t="s">
+      <c r="AB17" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="AB17" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="AC17" s="6" t="s">
         <v>89</v>
@@ -3193,13 +3190,13 @@
     </row>
     <row r="18" ht="72" spans="1:30">
       <c r="A18" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>69</v>
@@ -3214,14 +3211,14 @@
         <v>72</v>
       </c>
       <c r="H18" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L18" s="6" t="s">
         <v>75</v>
@@ -3234,16 +3231,16 @@
         <v>77</v>
       </c>
       <c r="P18" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R18" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Q18" s="6" t="s">
+      <c r="S18" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="S18" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="T18" s="6"/>
       <c r="U18" s="6" t="s">
@@ -3262,30 +3259,30 @@
         <v>85</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AB18" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AC18" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD18" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="72" spans="1:30">
       <c r="A19" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
         <v>192</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>193</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>69</v>
@@ -3300,10 +3297,10 @@
         <v>72</v>
       </c>
       <c r="H19" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
@@ -3312,22 +3309,22 @@
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P19" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="S19" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="R19" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="S19" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="T19" s="6"/>
       <c r="U19" s="6" t="s">
@@ -3346,30 +3343,30 @@
         <v>85</v>
       </c>
       <c r="Z19" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA19" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AB19" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD19" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:30">
       <c r="A20" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="C20" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>69</v>
@@ -3384,10 +3381,10 @@
         <v>72</v>
       </c>
       <c r="H20" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
@@ -3402,10 +3399,10 @@
         <v>77</v>
       </c>
       <c r="P20" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q20" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="R20" s="6"/>
       <c r="S20" s="6"/>
@@ -3426,30 +3423,30 @@
         <v>85</v>
       </c>
       <c r="Z20" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA20" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="AA20" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="AB20" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AC20" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD20" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" ht="72" spans="1:30">
       <c r="A21" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>69</v>
@@ -3464,10 +3461,10 @@
         <v>72</v>
       </c>
       <c r="H21" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>210</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>211</v>
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
@@ -3476,22 +3473,22 @@
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P21" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="R21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="S21" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="R21" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="S21" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="T21" s="6"/>
       <c r="U21" s="6" t="s">
@@ -3510,30 +3507,30 @@
         <v>85</v>
       </c>
       <c r="Z21" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AA21" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AB21" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AC21" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD21" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" ht="72" spans="1:30">
       <c r="A22" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>69</v>
@@ -3548,10 +3545,10 @@
         <v>72</v>
       </c>
       <c r="H22" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>215</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
@@ -3566,10 +3563,10 @@
         <v>77</v>
       </c>
       <c r="P22" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q22" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="Q22" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="R22" s="6"/>
       <c r="S22" s="6"/>
@@ -3590,19 +3587,19 @@
         <v>85</v>
       </c>
       <c r="Z22" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AB22" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AC22" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AD22" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
